--- a/AiSD/lab4/lab4.xlsx
+++ b/AiSD/lab4/lab4.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oleg5\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\AiSD\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8FA0998-F2E9-40C8-9CA7-D1231B8AD7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08E2A24-C826-4E8A-AC23-338176024B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="1180" windowWidth="17190" windowHeight="8860" xr2:uid="{03BFB3D7-7529-495F-AC52-7574DE19632C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" xr2:uid="{03BFB3D7-7529-495F-AC52-7574DE19632C}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -769,26 +778,24 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Лист1!$C$3:$C$8</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$C$6:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
@@ -796,26 +803,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$D$3:$D$8</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$D$3:$D$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$D$6:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1.502E-6</c:v>
+                  <c:v>2.3305400000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2753999999999999E-5</c:v>
+                  <c:v>5.0206000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.6928999999999994E-5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.3305400000000001E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.0206000000000003E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>8.6497699999999996E-4</c:v>
                 </c:pt>
               </c:numCache>
@@ -825,6 +830,89 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-F2BE-42F5-BCB8-8B62B33F82D7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Алгоритм Дейкстры</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$C$6:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$E$3:$E$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$E$6:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.5641999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5401000000000002E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.8247000000000001E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EA77-4495-AE47-76DEE4AFC10C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -839,6 +927,105 @@
         <c:smooth val="0"/>
         <c:axId val="680244384"/>
         <c:axId val="680237664"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Лист1!$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Алгоритм прямого перебора</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Лист1!$C$6:$C$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>Лист1!$I$3:$I$8</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Лист1!$I$6:$I$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>7.7700700000000002E-4</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.7700700000000004E-3</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3.8850350000000006E-2</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-EA77-4495-AE47-76DEE4AFC10C}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
       </c:lineChart>
       <c:catAx>
         <c:axId val="680244384"/>
@@ -1087,8 +1274,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.15258614809539231"/>
           <c:y val="8.9776525470633473E-2"/>
-          <c:w val="0.26383169784530164"/>
-          <c:h val="0.1266623562717504"/>
+          <c:w val="0.28011213209253555"/>
+          <c:h val="0.25647793675381059"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -1679,450 +1866,6 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Лист1!$I$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Алгоритм прямого перебора</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Лист1!$H$3:$H$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Лист1!$I$3:$I$8</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>3.2230000000000001E-5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4847999999999999E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.4973600000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.7700699999999996E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.7700699999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.3885035</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7C7E-48E5-B48D-5878922FB2E4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="680221824"/>
-        <c:axId val="680199264"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="680221824"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Количество вершин графа, шт.</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.31406842143922048"/>
-              <c:y val="0.89410921390724329"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="680199264"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="680199264"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Время, с</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="680221824"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.21049999999999999"/>
-          <c:y val="0.1533559346748323"/>
-          <c:w val="0.28116666666666668"/>
-          <c:h val="0.12847326900216208"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
         <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -2177,22 +1920,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.9338E-4</c:v>
+                  <c:v>1.9338E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.9087999999999993E-4</c:v>
+                  <c:v>8.9087999999999998E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.9841600000000015E-3</c:v>
+                  <c:v>8.9841599999999997E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.6620419999999996E-2</c:v>
+                  <c:v>4.6620419999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.46620419999999996</c:v>
+                  <c:v>4.6620420000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.3310209999999998</c:v>
+                  <c:v>0.23310210000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2519,6 +2262,618 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Алгоритм Дейкстры</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$C$5:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$E$3:$E$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$E$5:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.7425999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5641999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5401000000000002E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8247000000000001E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-8944-4F37-80C8-B068FFC47985}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$I$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Алгоритм прямого перебора</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$C$5:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$I$3:$I$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$I$5:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.49736E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7700700000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.7700700000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.8850350000000006E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-8944-4F37-80C8-B068FFC47985}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Алгоритм Флойда-Уоршелла</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$C$5:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Лист1!$D$3:$D$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Лист1!$D$5:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8.6928999999999994E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3305400000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0206000000000003E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6497699999999996E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-8944-4F37-80C8-B068FFC47985}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1193792592"/>
+        <c:axId val="1193793424"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Лист1!$C$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Количество вершин графа</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Лист1!$C$5:$C$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>Лист1!$C$3:$C$8</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Лист1!$C$5:$C$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-8944-4F37-80C8-B068FFC47985}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1193792592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1193793424"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1193793424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1193792592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="5.000000000000001E-2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11948861505948123"/>
+          <c:y val="0.87330314626702199"/>
+          <c:w val="0.76087683641817494"/>
+          <c:h val="7.0919554417357658E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2560,12 +2915,9 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -2680,12 +3032,9 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -5339,16 +5688,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>335617</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>403351</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>98986</xdr:rowOff>
+      <xdr:rowOff>31252</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>40528</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>565462</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>79936</xdr:rowOff>
+      <xdr:rowOff>12202</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5375,16 +5724,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>235136</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>93756</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>243602</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>119157</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>365499</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>74707</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>111499</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>100108</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5404,42 +5753,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582707</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>107576</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>254001</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>49306</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Диаграмма 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC642E5-8961-69E3-38DA-F797C6645B87}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5475,6 +5788,42 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Диаграмма 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B543D6F-5F63-458A-903C-806B81E12553}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
@@ -5482,6 +5831,135 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.56169</cdr:x>
+      <cdr:y>0.8626</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.94968</cdr:x>
+      <cdr:y>0.92621</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B780065C-9FE4-44CE-A769-3A8E74DC6392}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2636520" y="2583180"/>
+          <a:ext cx="1821180" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.21104</cdr:x>
+      <cdr:y>0.91349</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.6461</cdr:x>
+      <cdr:y>1</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFD0DFC7-3868-4747-A0C9-A8E689002308}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="990600" y="2735580"/>
+          <a:ext cx="2042160" cy="259080"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Алгоритм Флойда-Уоршелла</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.16756</cdr:x>
+      <cdr:y>0.94981</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.22603</cdr:x>
+      <cdr:y>0.96557</cdr:y>
+    </cdr:to>
+    <cdr:pic>
+      <cdr:nvPicPr>
+        <cdr:cNvPr id="4" name="chart">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B84293D-8A8B-4A79-9D1A-046010E7688B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cdr:cNvPicPr>
+      </cdr:nvPicPr>
+      <cdr:blipFill rotWithShape="1">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="22976" t="39813" b="-1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:blipFill>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="785831" y="2836759"/>
+          <a:ext cx="274228" cy="47073"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+    </cdr:pic>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5782,19 +6260,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1688FFF1-CAE4-403A-A7AB-1232774C2019}">
   <dimension ref="C1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="3:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
@@ -5812,7 +6290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C3" s="8">
         <v>5</v>
       </c>
@@ -5826,14 +6304,14 @@
         <v>5</v>
       </c>
       <c r="I3" s="12">
-        <v>3.2230000000000001E-5</v>
+        <v>3.2229999999999999E-6</v>
       </c>
       <c r="J3">
         <f>I3*6</f>
-        <v>1.9338E-4</v>
+        <v>1.9338E-5</v>
       </c>
     </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C4" s="8">
         <v>10</v>
       </c>
@@ -5847,14 +6325,14 @@
         <v>10</v>
       </c>
       <c r="I4" s="13">
-        <v>1.4847999999999999E-4</v>
+        <v>1.4848000000000001E-5</v>
       </c>
       <c r="J4">
         <f t="shared" ref="J4:J8" si="0">I4*6</f>
-        <v>8.9087999999999993E-4</v>
+        <v>8.9087999999999998E-5</v>
       </c>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C5" s="8">
         <v>15</v>
       </c>
@@ -5868,14 +6346,14 @@
         <v>15</v>
       </c>
       <c r="I5" s="13">
-        <v>1.4973600000000001E-3</v>
+        <v>1.49736E-4</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>8.9841600000000015E-3</v>
+        <v>8.9841599999999997E-4</v>
       </c>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" s="8">
         <v>20</v>
       </c>
@@ -5889,14 +6367,14 @@
         <v>20</v>
       </c>
       <c r="I6" s="13">
-        <v>7.7700699999999996E-3</v>
+        <v>7.7700700000000002E-4</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>4.6620419999999996E-2</v>
+        <v>4.6620419999999999E-3</v>
       </c>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" s="8">
         <v>25</v>
       </c>
@@ -5911,14 +6389,14 @@
       </c>
       <c r="I7" s="13">
         <f>I6*10</f>
-        <v>7.7700699999999998E-2</v>
+        <v>7.7700700000000004E-3</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.46620419999999996</v>
+        <v>4.6620420000000003E-2</v>
       </c>
     </row>
-    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="9">
         <v>30</v>
       </c>
@@ -5933,11 +6411,11 @@
       </c>
       <c r="I8" s="14">
         <f>I7*5</f>
-        <v>0.3885035</v>
+        <v>3.8850350000000006E-2</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>2.3310209999999998</v>
+        <v>0.23310210000000003</v>
       </c>
     </row>
   </sheetData>
